--- a/structure.xlsx
+++ b/structure.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nazarov.erbol\Desktop\ДАШБОРД\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nazarov.erbol\Desktop\ДАШБОРД\execution-discipline-FINAL-v7.2-simple-filters - не удалять\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39B4EC5-ECEC-4AE6-99C4-E21DB222F510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375850D1-619D-4096-BBD0-8F7F449DF5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -265,9 +265,6 @@
   </si>
   <si>
     <t>Саликов Асхат Муканович</t>
-  </si>
-  <si>
-    <t>Керей Динмухамед Болатович</t>
   </si>
   <si>
     <t xml:space="preserve">Хамзе Ділназ Еркінбекқызы </t>
@@ -582,6 +579,9 @@
   </si>
   <si>
     <t>Директора НОР</t>
+  </si>
+  <si>
+    <t>Керей Динмухамед Болатұлы</t>
   </si>
 </sst>
 </file>
@@ -1310,7 +1310,7 @@
   <sheetData>
     <row r="1" spans="1:1016" x14ac:dyDescent="0.25">
       <c r="A1" s="46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
@@ -1352,22 +1352,22 @@
         <v>0</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C4" s="42" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E4" s="43" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F4" s="45" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G4" s="45" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:1016" ht="47.25" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -1375,7 +1375,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>3</v>
@@ -1387,10 +1387,10 @@
     </row>
     <row r="6" spans="1:1016" ht="47.25" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>4</v>
@@ -1400,12 +1400,12 @@
       <c r="F6" s="18"/>
       <c r="G6" s="38"/>
     </row>
-    <row r="7" spans="1:1016" ht="78.75" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1016" ht="63" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
@@ -1420,7 +1420,7 @@
         <v>67</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>6</v>
@@ -1435,7 +1435,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>8</v>
@@ -1443,7 +1443,7 @@
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="F9" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G9" s="38"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>38</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C10" s="23" t="s">
         <v>9</v>
@@ -1461,10 +1461,10 @@
         <v>67</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G10" s="38"/>
     </row>
@@ -1473,7 +1473,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>12</v>
@@ -1482,7 +1482,7 @@
         <v>67</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F11" s="38"/>
       <c r="G11" s="38"/>
@@ -1492,7 +1492,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>14</v>
@@ -1501,17 +1501,17 @@
         <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F12" s="38"/>
       <c r="G12" s="38"/>
     </row>
     <row r="13" spans="1:1016" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>15</v>
@@ -1520,26 +1520,26 @@
         <v>67</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F13" s="38"/>
       <c r="G13" s="38"/>
     </row>
     <row r="14" spans="1:1016" ht="78.75" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D14" s="20" t="s">
         <v>67</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F14" s="38"/>
       <c r="G14" s="38"/>
@@ -1549,19 +1549,19 @@
         <v>16</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C15" s="23" t="s">
         <v>17</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G15" s="39"/>
       <c r="H15" s="7"/>
@@ -2579,35 +2579,35 @@
         <v>18</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F16" s="38"/>
       <c r="G16" s="38"/>
     </row>
     <row r="17" spans="1:1016" s="8" customFormat="1" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F17" s="39"/>
       <c r="G17" s="39"/>
@@ -3626,16 +3626,16 @@
         <v>19</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F18" s="38"/>
       <c r="G18" s="38"/>
@@ -3645,35 +3645,35 @@
         <v>20</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F19" s="38"/>
       <c r="G19" s="38"/>
     </row>
     <row r="20" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F20" s="38"/>
       <c r="G20" s="38"/>
@@ -3683,16 +3683,16 @@
         <v>21</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F21" s="39"/>
       <c r="G21" s="39"/>
@@ -4711,16 +4711,16 @@
         <v>28</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F22" s="38"/>
       <c r="G22" s="38"/>
@@ -4730,16 +4730,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F23" s="39"/>
       <c r="G23" s="39"/>
@@ -5755,76 +5755,76 @@
     </row>
     <row r="24" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F24" s="38"/>
       <c r="G24" s="38"/>
     </row>
     <row r="25" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F25" s="38"/>
       <c r="G25" s="38"/>
     </row>
     <row r="26" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F26" s="38"/>
       <c r="G26" s="38"/>
     </row>
     <row r="27" spans="1:1016" s="8" customFormat="1" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F27" s="39"/>
       <c r="G27" s="39"/>
@@ -6843,26 +6843,26 @@
         <v>24</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F28" s="38"/>
       <c r="G28" s="38"/>
     </row>
     <row r="29" spans="1:1016" s="8" customFormat="1" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -6871,10 +6871,10 @@
         <v>2</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G29" s="39"/>
       <c r="H29" s="7"/>
@@ -7889,10 +7889,10 @@
     </row>
     <row r="30" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>15</v>
@@ -7901,17 +7901,17 @@
         <v>2</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F30" s="38"/>
       <c r="G30" s="38"/>
     </row>
     <row r="31" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A31" s="29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B31" s="29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>15</v>
@@ -7920,29 +7920,29 @@
         <v>2</v>
       </c>
       <c r="E31" s="29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F31" s="38"/>
       <c r="G31" s="38"/>
     </row>
     <row r="32" spans="1:1016" s="8" customFormat="1" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G32" s="39"/>
       <c r="H32" s="7"/>
@@ -8188,7 +8188,7 @@
       <c r="IN32" s="7"/>
       <c r="IO32" s="7"/>
       <c r="IP32" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="IQ32" s="7"/>
       <c r="IR32" s="7"/>
@@ -8962,16 +8962,16 @@
         <v>26</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F33" s="38"/>
       <c r="G33" s="38"/>
@@ -8981,16 +8981,16 @@
         <v>27</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F34" s="38"/>
       <c r="G34" s="38"/>
@@ -9000,7 +9000,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C35" s="23" t="s">
         <v>17</v>
@@ -9009,10 +9009,10 @@
         <v>67</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G35" s="41"/>
     </row>
@@ -9021,7 +9021,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>14</v>
@@ -9030,26 +9030,26 @@
         <v>67</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F36" s="40"/>
       <c r="G36" s="40"/>
     </row>
     <row r="37" spans="1:1016" s="9" customFormat="1" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="B37" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="D37" s="20" t="s">
         <v>67</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F37" s="40"/>
       <c r="G37" s="40"/>
@@ -9059,7 +9059,7 @@
         <v>31</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C38" s="11" t="s">
         <v>14</v>
@@ -9068,7 +9068,7 @@
         <v>67</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F38" s="39"/>
       <c r="G38" s="39"/>
@@ -10087,7 +10087,7 @@
         <v>32</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>15</v>
@@ -10096,7 +10096,7 @@
         <v>67</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F39" s="38"/>
       <c r="G39" s="38"/>
@@ -10106,7 +10106,7 @@
         <v>33</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>14</v>
@@ -10115,7 +10115,7 @@
         <v>67</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F40" s="39"/>
       <c r="G40" s="39"/>
@@ -11134,16 +11134,16 @@
         <v>34</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D41" s="20" t="s">
         <v>67</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F41" s="38"/>
       <c r="G41" s="38"/>
@@ -11153,7 +11153,7 @@
         <v>35</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C42" s="11" t="s">
         <v>14</v>
@@ -11162,7 +11162,7 @@
         <v>67</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F42" s="39"/>
       <c r="G42" s="39"/>
@@ -12181,7 +12181,7 @@
         <v>36</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>15</v>
@@ -12190,17 +12190,17 @@
         <v>67</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F43" s="38"/>
       <c r="G43" s="38"/>
     </row>
     <row r="44" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>15</v>
@@ -12209,17 +12209,17 @@
         <v>67</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F44" s="38"/>
       <c r="G44" s="38"/>
     </row>
     <row r="45" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A45" s="37" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C45" s="19" t="s">
         <v>17</v>
@@ -12228,17 +12228,17 @@
         <v>2</v>
       </c>
       <c r="E45" s="37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F45" s="38"/>
       <c r="G45" s="38"/>
     </row>
     <row r="46" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C46" s="26" t="s">
         <v>37</v>
@@ -12247,17 +12247,17 @@
         <v>2</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F46" s="38"/>
       <c r="G46" s="38"/>
     </row>
     <row r="47" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C47" s="32" t="s">
         <v>14</v>
@@ -12266,17 +12266,17 @@
         <v>2</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F47" s="38"/>
       <c r="G47" s="38"/>
     </row>
     <row r="48" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A48" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C48" s="32" t="s">
         <v>15</v>
@@ -12285,17 +12285,17 @@
         <v>2</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F48" s="38"/>
       <c r="G48" s="38"/>
     </row>
     <row r="49" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A49" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C49" s="32" t="s">
         <v>39</v>
@@ -12304,14 +12304,14 @@
         <v>2</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F49" s="38"/>
       <c r="G49" s="38"/>
     </row>
     <row r="50" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B50" s="13" t="s">
         <v>65</v>
@@ -12332,90 +12332,90 @@
     </row>
     <row r="51" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="D51" s="30" t="s">
         <v>2</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F51" s="38"/>
       <c r="G51" s="38"/>
     </row>
     <row r="52" spans="1:1016" ht="63" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A52" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="C52" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D52" s="30" t="s">
         <v>2</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G52" s="38"/>
     </row>
     <row r="53" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A53" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="C53" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D53" s="30" t="s">
         <v>2</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G53" s="38"/>
     </row>
     <row r="54" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A54" s="27" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D54" s="30" t="s">
         <v>2</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="38"/>
     </row>
     <row r="55" spans="1:1016" s="8" customFormat="1" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C55" s="23" t="s">
         <v>17</v>
@@ -12424,10 +12424,10 @@
         <v>2</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G55" s="39"/>
       <c r="H55" s="7"/>
@@ -13442,10 +13442,10 @@
     </row>
     <row r="56" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>15</v>
@@ -13454,7 +13454,7 @@
         <v>2</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F56" s="38"/>
       <c r="G56" s="38"/>
@@ -13464,7 +13464,7 @@
         <v>40</v>
       </c>
       <c r="B57" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>14</v>
@@ -13473,7 +13473,7 @@
         <v>2</v>
       </c>
       <c r="E57" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F57" s="38"/>
       <c r="G57" s="38"/>
@@ -13483,7 +13483,7 @@
         <v>41</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>15</v>
@@ -13492,7 +13492,7 @@
         <v>2</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F58" s="38"/>
       <c r="G58" s="38"/>
@@ -13502,7 +13502,7 @@
         <v>42</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C59" s="27" t="s">
         <v>15</v>
@@ -13511,17 +13511,17 @@
         <v>2</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F59" s="38"/>
       <c r="G59" s="38"/>
     </row>
     <row r="60" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A60" s="34" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B60" s="34" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C60" s="26" t="s">
         <v>14</v>
@@ -13530,26 +13530,26 @@
         <v>2</v>
       </c>
       <c r="E60" s="34" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F60" s="38"/>
       <c r="G60" s="38"/>
     </row>
     <row r="61" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A61" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="B61" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="C61" s="26" t="s">
         <v>109</v>
-      </c>
-      <c r="B61" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="C61" s="26" t="s">
-        <v>110</v>
       </c>
       <c r="D61" s="30" t="s">
         <v>2</v>
       </c>
       <c r="E61" s="34" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F61" s="38"/>
       <c r="G61" s="38"/>
@@ -13559,19 +13559,19 @@
         <v>43</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F62" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G62" s="38"/>
     </row>
@@ -13580,16 +13580,16 @@
         <v>44</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D63" s="24" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F63" s="39"/>
       <c r="G63" s="39"/>
@@ -14608,16 +14608,16 @@
         <v>45</v>
       </c>
       <c r="B64" s="35" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D64" s="20" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E64" s="35" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F64" s="38"/>
       <c r="G64" s="38"/>
@@ -14627,16 +14627,16 @@
         <v>46</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D65" s="24" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F65" s="39"/>
       <c r="G65" s="39"/>
@@ -15655,35 +15655,35 @@
         <v>47</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D66" s="20" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F66" s="38"/>
       <c r="G66" s="38"/>
     </row>
     <row r="67" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D67" s="20" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F67" s="38"/>
       <c r="G67" s="38"/>
@@ -15693,16 +15693,16 @@
         <v>48</v>
       </c>
       <c r="B68" s="25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D68" s="24" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E68" s="25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F68" s="39"/>
       <c r="G68" s="39"/>
@@ -16721,16 +16721,16 @@
         <v>49</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D69" s="24" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F69" s="39"/>
       <c r="G69" s="39"/>
@@ -17749,19 +17749,19 @@
         <v>50</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D70" s="20" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G70" s="38"/>
     </row>
@@ -17770,35 +17770,35 @@
         <v>52</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D71" s="20" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F71" s="38"/>
       <c r="G71" s="38"/>
     </row>
     <row r="72" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A72" s="29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B72" s="29" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D72" s="20" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E72" s="29" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F72" s="38"/>
       <c r="G72" s="38"/>
@@ -17808,73 +17808,73 @@
         <v>53</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D73" s="20" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F73" s="38"/>
       <c r="G73" s="38"/>
     </row>
     <row r="74" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D74" s="20" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F74" s="38"/>
       <c r="G74" s="38"/>
     </row>
     <row r="75" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A75" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D75" s="20" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F75" s="38"/>
       <c r="G75" s="38"/>
     </row>
     <row r="76" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A76" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D76" s="20" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F76" s="38"/>
       <c r="G76" s="38"/>
@@ -17884,35 +17884,35 @@
         <v>54</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D77" s="20" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F77" s="38"/>
       <c r="G77" s="38"/>
     </row>
     <row r="78" spans="1:1016" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A78" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D78" s="20" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F78" s="38"/>
       <c r="G78" s="38"/>
@@ -17922,19 +17922,19 @@
         <v>55</v>
       </c>
       <c r="B79" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C79" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D79" s="20" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F79" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G79" s="38"/>
     </row>
@@ -17943,16 +17943,16 @@
         <v>56</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D80" s="24" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F80" s="39"/>
       <c r="G80" s="39"/>
@@ -18971,16 +18971,16 @@
         <v>57</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D81" s="20" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F81" s="38"/>
       <c r="G81" s="38"/>
@@ -18990,16 +18990,16 @@
         <v>58</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D82" s="20" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F82" s="38"/>
       <c r="G82" s="38"/>
@@ -19009,16 +19009,16 @@
         <v>59</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>60</v>
       </c>
       <c r="D83" s="24" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F83" s="39"/>
       <c r="G83" s="39"/>
@@ -20037,16 +20037,16 @@
         <v>61</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D84" s="20" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F84" s="38"/>
       <c r="G84" s="38"/>
@@ -20056,35 +20056,35 @@
         <v>62</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D85" s="20" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F85" s="38"/>
       <c r="G85" s="38"/>
     </row>
     <row r="86" spans="1:1016" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A86" s="36" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B86" s="36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D86" s="20" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E86" s="36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F86" s="38"/>
       <c r="G86" s="38"/>
@@ -20092,19 +20092,19 @@
     </row>
     <row r="87" spans="1:1016" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D87" s="20" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F87" s="38"/>
       <c r="G87" s="38"/>
@@ -20114,7 +20114,7 @@
     <row r="88" spans="1:1016" s="8" customFormat="1" ht="47.25" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A88" s="11"/>
       <c r="B88" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C88" s="11" t="s">
         <v>63</v>
@@ -20123,10 +20123,10 @@
         <v>2</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G88" s="39"/>
       <c r="H88" s="7"/>
@@ -21141,10 +21141,10 @@
     </row>
     <row r="89" spans="1:1016" s="8" customFormat="1" ht="47.25" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A89" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C89" s="11" t="s">
         <v>64</v>
@@ -21153,10 +21153,10 @@
         <v>2</v>
       </c>
       <c r="E89" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G89" s="39"/>
       <c r="H89" s="7"/>
@@ -22174,16 +22174,16 @@
         <v>25</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D90" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F90" s="39"/>
       <c r="G90" s="39"/>
@@ -23199,19 +23199,19 @@
     </row>
     <row r="91" spans="1:1016" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="D91" s="20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F91" s="38"/>
       <c r="G91" s="38"/>
@@ -23220,17 +23220,17 @@
     </row>
     <row r="92" spans="1:1016" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="D92" s="20"/>
       <c r="E92" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F92" s="38"/>
       <c r="G92" s="38"/>
@@ -23239,216 +23239,216 @@
     </row>
     <row r="93" spans="1:1016" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D93" s="20"/>
       <c r="E93" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F93" s="38"/>
       <c r="G93" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AMA93" s="6"/>
       <c r="AMB93" s="6"/>
     </row>
     <row r="94" spans="1:1016" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D94" s="20"/>
       <c r="E94" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F94" s="38"/>
       <c r="G94" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AMA94" s="6"/>
       <c r="AMB94" s="6"/>
     </row>
     <row r="95" spans="1:1016" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D95" s="20"/>
       <c r="E95" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F95" s="38"/>
       <c r="G95" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AMB95" s="6"/>
     </row>
     <row r="96" spans="1:1016" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D96" s="20"/>
       <c r="E96" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F96" s="38"/>
       <c r="G96" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D97" s="20"/>
       <c r="E97" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F97" s="38"/>
       <c r="G97" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D98" s="20"/>
       <c r="E98" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F98" s="38"/>
       <c r="G98" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D99" s="20"/>
       <c r="E99" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F99" s="38"/>
       <c r="G99" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D100" s="20"/>
       <c r="E100" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F100" s="38"/>
       <c r="G100" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="101" spans="1:7" s="5" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D101" s="20"/>
       <c r="E101" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F101" s="38"/>
       <c r="G101" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="102" spans="1:7" s="5" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D102" s="20"/>
       <c r="E102" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F102" s="38"/>
       <c r="G102" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="103" spans="1:7" s="5" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D103" s="20"/>
       <c r="E103" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F103" s="38"/>
       <c r="G103" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="104" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
